--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6195331</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112076813</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -969,6 +984,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112076818</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128654619</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112076812</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113057263</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1408,6 +1443,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112076815</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1505,6 +1545,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112076816</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,6 +1647,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112076817</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128654616</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1813,6 +1868,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112431163</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1914,6 +1974,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112422051</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2015,6 +2080,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112431067</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2122,6 +2192,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117485775</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2216,6 +2291,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111724737</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2318,6 +2398,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/220705</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2421,6 +2506,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85978792</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2528,6 +2618,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85978813</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2635,6 +2730,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85978842</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2738,6 +2838,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85978872</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2865,6 +2970,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116620214</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2966,8 +3076,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79420805</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ23"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1349,48 +1349,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112076815</v>
+        <v>136152858</v>
       </c>
       <c r="B8" t="n">
-        <v>99118</v>
+        <v>80564</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>spikbodarna, Jmt</t>
+          <t>Spikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485636</v>
+        <v>485743</v>
       </c>
       <c r="R8" t="n">
-        <v>7005629</v>
+        <v>7005475</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1414,12 +1414,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,65 +1449,65 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ingo Strassmann</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ingo Strassmann</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112076815</t>
+          <t>https://artportalen.se/Sighting/136152858</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112076816</v>
+        <v>136152860</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>80564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>spikbodarna, Jmt</t>
+          <t>Spikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485618</v>
+        <v>485591</v>
       </c>
       <c r="R9" t="n">
-        <v>7005614</v>
+        <v>7005590</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1516,12 +1531,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,24 +1561,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ingo Strassmann</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ingo Strassmann</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112076816</t>
+          <t>https://artportalen.se/Sighting/136152860</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112076817</v>
+        <v>112076815</v>
       </c>
       <c r="B10" t="n">
         <v>99118</v>
@@ -1588,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485596</v>
+        <v>485636</v>
       </c>
       <c r="R10" t="n">
-        <v>7005613</v>
+        <v>7005629</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,13 +1674,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112076817</t>
+          <t>https://artportalen.se/Sighting/112076815</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128654616</v>
+        <v>112076816</v>
       </c>
       <c r="B11" t="n">
         <v>99118</v>
@@ -1683,32 +1708,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Spikbodarna, Östersund, Jmt</t>
+          <t>spikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485635</v>
+        <v>485618</v>
       </c>
       <c r="R11" t="n">
-        <v>7005628</v>
+        <v>7005614</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1732,12 +1745,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,75 +1759,71 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Christer Pålsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Christer Pålsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128654616</t>
+          <t>https://artportalen.se/Sighting/112076816</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112431163</v>
+        <v>112076817</v>
       </c>
       <c r="B12" t="n">
-        <v>89018</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>797</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lilavaxing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cuphophyllus flavipes</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Britzelm.) Bon</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kraftledningsgata norr om Småbodarna, Jmt</t>
+          <t>spikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485894</v>
+        <v>485596</v>
       </c>
       <c r="R12" t="n">
-        <v>7005070</v>
+        <v>7005613</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1838,12 +1847,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,72 +1861,80 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112431163</t>
+          <t>https://artportalen.se/Sighting/112076817</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112422051</v>
+        <v>128654616</v>
       </c>
       <c r="B13" t="n">
-        <v>89092</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2017</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Slemvaxing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hygrocybe glutinipes</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(J.E.Lange) R.Haller Aar.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kraftledningsgata norr om Småbodarna, Jmt</t>
+          <t>Spikbodarna, Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485894</v>
+        <v>485635</v>
       </c>
       <c r="R13" t="n">
-        <v>7005070</v>
+        <v>7005628</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1944,12 +1961,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,49 +1982,49 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Christer Pålsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Christer Pålsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112422051</t>
+          <t>https://artportalen.se/Sighting/128654616</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112431067</v>
+        <v>112431163</v>
       </c>
       <c r="B14" t="n">
-        <v>89081</v>
+        <v>89018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4374</v>
+        <v>797</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulvaxing</t>
+          <t>Lilavaxing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hygrocybe chlorophana</t>
+          <t>Cuphophyllus flavipes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Wünsche</t>
+          <t>(Britzelm.) Bon</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2082,54 +2099,57 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112431067</t>
+          <t>https://artportalen.se/Sighting/112431163</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117485775</v>
+        <v>112422051</v>
       </c>
       <c r="B15" t="n">
-        <v>43249</v>
+        <v>89092</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101248</v>
+        <v>2017</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violett guldvinge</t>
+          <t>Slemvaxing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycaena helle</t>
+          <t>Hygrocybe glutinipes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(J.E.Lange) R.Haller Aar.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kraftledningsgata mellan Småbodarna och Mårtensbodarna, Jmt</t>
+          <t>Kraftledningsgata norr om Småbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485862</v>
+        <v>485894</v>
       </c>
       <c r="R15" t="n">
-        <v>7005052</v>
+        <v>7005070</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2153,22 +2173,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:26</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:26</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2177,6 +2187,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2194,48 +2205,54 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117485775</t>
+          <t>https://artportalen.se/Sighting/112422051</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111724737</v>
+        <v>112431067</v>
       </c>
       <c r="B16" t="n">
-        <v>106414</v>
+        <v>89081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221447</v>
+        <v>4374</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Gulvaxing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Hygrocybe chlorophana</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Wünsche</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kraftlefningsgata mellan Småbodarna och Mårtensbodarna, Jmt</t>
+          <t>Kraftledningsgata norr om Småbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485814</v>
+        <v>485894</v>
       </c>
       <c r="R16" t="n">
-        <v>7005042</v>
+        <v>7005070</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2262,12 +2279,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2276,6 +2293,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2293,16 +2311,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111724737</t>
+          <t>https://artportalen.se/Sighting/112431067</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>220705</v>
+        <v>117485775</v>
       </c>
       <c r="B17" t="n">
-        <v>106415</v>
+        <v>43249</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2310,34 +2328,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>698</v>
+        <v>101248</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sen fältgentiana</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gentianella campestris var. campestris</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>Lycaena helle</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Småbodarna, Östersund, Jmt</t>
+          <t>Kraftledningsgata mellan Småbodarna och Mårtensbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485090</v>
+        <v>485862</v>
       </c>
       <c r="R17" t="n">
-        <v>7004828</v>
+        <v>7005052</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2364,12 +2382,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2003-08-15</t>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2003-08-15</t>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,36 +2408,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Kraftledningsgata</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/220705</t>
+          <t>https://artportalen.se/Sighting/117485775</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>85978792</v>
+        <v>111724737</v>
       </c>
       <c r="B18" t="n">
-        <v>43249</v>
+        <v>106414</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,39 +2440,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101248</v>
+        <v>221447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violett guldvinge</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycaena helle</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Östersund, Jmt</t>
+          <t>Kraftlefningsgata mellan Småbodarna och Mårtensbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485091</v>
+        <v>485814</v>
       </c>
       <c r="R18" t="n">
-        <v>7004966</v>
+        <v>7005042</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2476,12 +2491,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2490,34 +2505,33 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85978792</t>
+          <t>https://artportalen.se/Sighting/111724737</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>85978813</v>
+        <v>220705</v>
       </c>
       <c r="B19" t="n">
-        <v>43249</v>
+        <v>106415</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2525,46 +2539,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101248</v>
+        <v>698</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violett guldvinge</t>
+          <t>Sen fältgentiana</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycaena helle</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
+          <t>Gentianella campestris var. campestris</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Östersund, Jmt</t>
+          <t>Småbodarna, Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>485096</v>
+        <v>485090</v>
       </c>
       <c r="R19" t="n">
-        <v>7004944</v>
+        <v>7004828</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2588,12 +2593,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2003-08-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2003-08-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2602,31 +2607,35 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kraftledningsgata</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85978813</t>
+          <t>https://artportalen.se/Sighting/220705</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>85978842</v>
+        <v>85978792</v>
       </c>
       <c r="B20" t="n">
         <v>43249</v>
@@ -2654,11 +2663,7 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -2673,7 +2678,7 @@
         <v>485091</v>
       </c>
       <c r="R20" t="n">
-        <v>7004877</v>
+        <v>7004966</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2732,13 +2737,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85978842</t>
+          <t>https://artportalen.se/Sighting/85978792</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>85978872</v>
+        <v>85978813</v>
       </c>
       <c r="B21" t="n">
         <v>43249</v>
@@ -2766,7 +2771,11 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -2778,10 +2787,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>485100</v>
+        <v>485096</v>
       </c>
       <c r="R21" t="n">
-        <v>7004799</v>
+        <v>7004944</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2840,71 +2849,60 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85978872</t>
+          <t>https://artportalen.se/Sighting/85978813</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>116620214</v>
+        <v>85978842</v>
       </c>
       <c r="B22" t="n">
-        <v>58327</v>
+        <v>43249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>101248</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Spikbodarna, Jmt</t>
+          <t>Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>485575</v>
+        <v>485091</v>
       </c>
       <c r="R22" t="n">
-        <v>7005187</v>
+        <v>7004877</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2931,12 +2929,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,82 +2943,74 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Grandominerad, flerskiktad och luckig äldre skog med fältskikt dominerat av blåbärs- och lingonris. På frisk-fuktig mark.</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116620214</t>
+          <t>https://artportalen.se/Sighting/85978842</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>79420805</v>
+        <v>85978872</v>
       </c>
       <c r="B23" t="n">
-        <v>109815</v>
+        <v>43249</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220204</v>
+        <v>101248</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Spikbodarna, 510 m SSV om intill stig, Jmt</t>
+          <t>Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>485178</v>
+        <v>485100</v>
       </c>
       <c r="R23" t="n">
-        <v>7005053</v>
+        <v>7004799</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3047,12 +3037,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2019-08-14</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2019-08-14</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3061,22 +3051,261 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85978872</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>116620214</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Spikbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>485575</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7005187</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Grandominerad, flerskiktad och luckig äldre skog med fältskikt dominerat av blåbärs- och lingonris. På frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116620214</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>79420805</v>
+      </c>
+      <c r="B25" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Spikbodarna, 510 m SSV om intill stig, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>485178</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7005053</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2019-08-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2019-08-14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/79420805</t>
         </is>
@@ -3106,6 +3335,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -1352,7 +1352,7 @@
         <v>136152858</v>
       </c>
       <c r="B8" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>136152860</v>
       </c>
       <c r="B9" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -1352,7 +1352,7 @@
         <v>136152858</v>
       </c>
       <c r="B8" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>136152860</v>
       </c>
       <c r="B9" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -1352,7 +1352,7 @@
         <v>136152858</v>
       </c>
       <c r="B8" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>136152860</v>
       </c>
       <c r="B9" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -1352,7 +1352,7 @@
         <v>136152858</v>
       </c>
       <c r="B8" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>136152860</v>
       </c>
       <c r="B9" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -1352,7 +1352,7 @@
         <v>136152858</v>
       </c>
       <c r="B8" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>136152860</v>
       </c>
       <c r="B9" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -1352,7 +1352,7 @@
         <v>136152858</v>
       </c>
       <c r="B8" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>136152860</v>
       </c>
       <c r="B9" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -1352,7 +1352,7 @@
         <v>136152858</v>
       </c>
       <c r="B8" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>136152860</v>
       </c>
       <c r="B9" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
